--- a/AAII_Financials/Yearly/WIT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WIT_YR_FIN.xlsx
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9878200</v>
+      </c>
+      <c r="E8" s="3">
         <v>10426200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10773100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11018800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10422100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8466800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8104000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8455600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8373000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6637800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6195400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6066500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5966900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4947700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4609100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6998100</v>
+      </c>
+      <c r="E9" s="3">
         <v>7230300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7579300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7859700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7324700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5784600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5791300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5961400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5925100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4722000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4312800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4151000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4060000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3446000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3265000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2880000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3195900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3193800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3159100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3097400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2682100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2312700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2494200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2447900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1915800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1882600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1915500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1906900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1501700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1344100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,28 +899,29 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E12" s="3">
         <v>50400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>44800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>38600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>50600</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,44 +998,47 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-101200</v>
+        <v>-84200</v>
       </c>
       <c r="E14" s="3">
+        <v>-122300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-52600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-14300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-42100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-21400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-41100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-21700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-75900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-12400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1030,44 +1049,47 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>229600</v>
+      </c>
+      <c r="E15" s="3">
         <v>261200</v>
       </c>
-      <c r="E15" s="3">
-        <v>281200</v>
-      </c>
       <c r="F15" s="3">
+        <v>388500</v>
+      </c>
+      <c r="G15" s="3">
         <v>384600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>407300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>378000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>277100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>247600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>314700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>38300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21000</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8655700</v>
+        <v>8282400</v>
       </c>
       <c r="E17" s="3">
+        <v>8676800</v>
+      </c>
+      <c r="F17" s="3">
         <v>9143400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9371900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8651300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6813400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6757200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7048500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7090600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5505700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5024400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4833700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4739100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4022600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3742800</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1770500</v>
+        <v>1595800</v>
       </c>
       <c r="E18" s="3">
+        <v>1749400</v>
+      </c>
+      <c r="F18" s="3">
         <v>1629800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1647000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1770900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1653400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1346800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1407100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1282400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1132200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1171000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1232900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1227700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>925000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>866300</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,88 +1244,92 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E20" s="3">
         <v>61300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>50200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-26300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-77700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-31900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-13400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-20400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>221800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>235500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>220000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>172000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>125400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>94700</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1970500</v>
+        <v>1776800</v>
       </c>
       <c r="E21" s="3">
-        <v>1860800</v>
+        <v>1949300</v>
       </c>
       <c r="F21" s="3">
+        <v>1968000</v>
+      </c>
+      <c r="G21" s="3">
         <v>2057900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2255900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2063300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1637300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1675100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1583600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1632900</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
@@ -1304,156 +1340,168 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>1107600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E22" s="3">
         <v>108200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>99100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>95300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>70200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>58700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>68200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>81100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>53000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13500</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1849500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2047600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1766800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1798000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1993400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1900000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1627000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1665800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1574700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1330900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1389500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1442900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1387800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1039000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>947500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>434800</v>
+      </c>
+      <c r="E24" s="3">
         <v>500600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>433100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>413900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>381400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>414800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>329300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>364300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>344100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>304100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>306700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>318100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>310500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>223600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>187300</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1414700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1546900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1333700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1384100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1611900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1485300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1297700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1301500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1230600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1026800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1082900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1124800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1077300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>815500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>760100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1407500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1537300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1325700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1382100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1610100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1475500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1291100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1299400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1230600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1023800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1076900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1117900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1071300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>811200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>756600</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,27 +1733,30 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>66100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>49200</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-61300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-50200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>26300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>77700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>31900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>13400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>20400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-221800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-235500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-220000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-172000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-125400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-94700</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1407500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1537300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1325700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1382100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1610100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1475500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1291100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1299400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1230600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1023800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1076900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1117900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1071300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>877300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>805900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1407500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1537300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1325700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1382100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1610100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1475500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1291100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1299400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1230600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1023800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1076900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1117900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1071300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>877300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>805900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1125700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1427500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1163600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1118800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1368200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2320800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1919000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2288100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>690400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>635700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1197500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2053500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1569100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>472100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>594900</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4667800</v>
+      </c>
+      <c r="E42" s="3">
         <v>4813100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3730700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3757600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3175700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2393300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2507800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3178900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3827800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3542800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5797800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1234800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1045300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1598900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1164500</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2628700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2473600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2510000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2710000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2734200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1995200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2077700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2177400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2354200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1886500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3217900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1949900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1937400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1631600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1744700</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E44" s="3">
         <v>8100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>57000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>51800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>64700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>65200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>62600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>65100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>43200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>154200</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>183300</v>
+      </c>
+      <c r="E45" s="3">
         <v>182100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>183200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>216000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>675200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>261700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>243300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>377700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>853900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>369400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>347500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>338600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>256400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>321300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>296300</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8812900</v>
+      </c>
+      <c r="E46" s="3">
         <v>9102500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7809300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8050300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8179600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7151200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6903800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8254400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7778000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6499100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6079200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5639500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4873400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4066900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3954600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>321900</v>
+      </c>
+      <c r="E47" s="3">
         <v>325200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>272100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>261800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>262000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>164500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>141800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>117600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>136400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>310900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>253700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>197400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>176800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>142000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>231700</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1173900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1243800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1195000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1307400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1446400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1388900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1299700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1019000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>990300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>841700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>785400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>700300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>706900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>668400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>853000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4442700</v>
+      </c>
+      <c r="E49" s="3">
         <v>4125000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4185700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4274400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3828500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2080500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1957200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1887000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2085200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1709100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1424600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>982000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>898000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>747100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1043500</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>165800</v>
+      </c>
+      <c r="E52" s="3">
         <v>147600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>217800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>291600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>309500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>402800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>299400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>516500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>482200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>208900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>210500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>233200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>246500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>193200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>221700</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15136100</v>
+      </c>
+      <c r="E54" s="3">
         <v>15056400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13832000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14318200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14220400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11364600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10850800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12025300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11688700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9569800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8753200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7752400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6901700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5817600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6304600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>237400</v>
+      </c>
+      <c r="E57" s="3">
         <v>257300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>279300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>264600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>378000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>317600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>359300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>411700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1046900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>282800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1107900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>243500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>242000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>204200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>338800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1862300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1239200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1060800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1186600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1374200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1141900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1059300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1026200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1429000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1481000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2608100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>855400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>559000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>833000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>527000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1057600</v>
+      </c>
+      <c r="E59" s="3">
         <v>717700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>541100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>635900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1037900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>633100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>547500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>569400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>805000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1004500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1054900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1020400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1073900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>877700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>835900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300400</v>
+      </c>
+      <c r="E60" s="3">
         <v>3350100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3030000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3260500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4062900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3144300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2873800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3093700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3280900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2768300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2642400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2119300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1874900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1914900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1701700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>301700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1008200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>915300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>940400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>944000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>286600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>232100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>409400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>695600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>236500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>209900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>164200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>149900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>325500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>825800</v>
+      </c>
+      <c r="E62" s="3">
         <v>735800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>610100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>377400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>338400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>248000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>229300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>205000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>206800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>261300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>250200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>176600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>138100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>121100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>139400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5667100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5337500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4815700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4798700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5541000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3784000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3422700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3787500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4230400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3294900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3129300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2481300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2182000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2062800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2178900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8116100</v>
+      </c>
+      <c r="E72" s="3">
         <v>8710200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8078200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8632300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7898800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6956900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6913100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7717400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6965300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5981300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5169200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4826400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4327400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3466000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3507000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9442300</v>
+      </c>
+      <c r="E76" s="3">
         <v>9693900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9000200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9512400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8672500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7560100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7403200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8199700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7421200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6274900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5623900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5271100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4719700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3754800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4125600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1407500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1537300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1325700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1382100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1610100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1475500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1291100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1299400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1230600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1023800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1076900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1117900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1071300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>877300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>805900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,40 +4083,41 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>227400</v>
+      </c>
+      <c r="E83" s="3">
         <v>253600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>267800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>384600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>407300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>378000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>277100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>247600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>314700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>278700</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
@@ -3930,12 +4128,15 @@
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>146500</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1592400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1982800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2115000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1590400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1460000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2016800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1336600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1678800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1294400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1118800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>946200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>877200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>932900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>931000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>579500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-166400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-172500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-126100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-180600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-265600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-267600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-312000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-328800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-336100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-251500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-153100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-115200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-122500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-140300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-187600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,41 +4611,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-356400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-944800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>140200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1023700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2958200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>105800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>451700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>723500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>546700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1402400</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
@@ -4430,12 +4659,15 @@
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>-116500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1228600</v>
+      </c>
+      <c r="E96" s="3">
         <v>734400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>62600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>399600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>72000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>74600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>75600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>65000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>83300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-105300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-356500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-300700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-319800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-225800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-249100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,41 +4887,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1506500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-748600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2191200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-741400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>613900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1761100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2005300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-712500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1997400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-274400</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
@@ -4690,44 +4935,47 @@
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>-251600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E101" s="3">
         <v>3400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>28900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>16900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>25500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17000</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
@@ -4738,58 +4986,64 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>24300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-175100</v>
+      </c>
+      <c r="E102" s="3">
         <v>292800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>61100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-145800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-867400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>349400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-191500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1697300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-150500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-574900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>538200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>388700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>413300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>91400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>235700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
